--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.61895286295965</v>
+        <v>13.91307984023094</v>
       </c>
       <c r="D2" t="n">
-        <v>85.23000334500459</v>
+        <v>13.84987554356325</v>
       </c>
       <c r="E2" t="n">
-        <v>10.77036438261556</v>
+        <v>1.750184212175028</v>
       </c>
       <c r="F2" t="n">
-        <v>10.8313427357807</v>
+        <v>1.760093194564365</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.0981243129642</v>
+        <v>10.57844520085668</v>
       </c>
       <c r="D3" t="n">
-        <v>64.71262858682186</v>
+        <v>10.51580214535855</v>
       </c>
       <c r="E3" t="n">
-        <v>10.77036438261556</v>
+        <v>1.750184212175028</v>
       </c>
       <c r="F3" t="n">
-        <v>10.8313427357807</v>
+        <v>1.760093194564365</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>78.68999608125691</v>
+        <v>12.78712436320425</v>
       </c>
       <c r="D4" t="n">
-        <v>78.8657349881215</v>
+        <v>12.81568193556974</v>
       </c>
       <c r="E4" t="n">
-        <v>10.77036438261556</v>
+        <v>1.750184212175028</v>
       </c>
       <c r="F4" t="n">
-        <v>10.8313427357807</v>
+        <v>1.760093194564365</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>92.45185277422152</v>
+        <v>15.023426075811</v>
       </c>
       <c r="D5" t="n">
-        <v>92.73716922364883</v>
+        <v>15.06978999884294</v>
       </c>
       <c r="E5" t="n">
-        <v>10.77036438261556</v>
+        <v>1.750184212175028</v>
       </c>
       <c r="F5" t="n">
-        <v>10.8313427357807</v>
+        <v>1.760093194564365</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.15178850927093</v>
+        <v>10.26216563275653</v>
       </c>
       <c r="D6" t="n">
-        <v>63.17722802186858</v>
+        <v>10.26629955355364</v>
       </c>
       <c r="E6" t="n">
-        <v>10.77036438261556</v>
+        <v>1.750184212175028</v>
       </c>
       <c r="F6" t="n">
-        <v>10.8313427357807</v>
+        <v>1.760093194564365</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>83.45171256396353</v>
+        <v>13.56090329164407</v>
       </c>
       <c r="D7" t="n">
-        <v>83.85361453292947</v>
+        <v>13.62621236160104</v>
       </c>
       <c r="E7" t="n">
-        <v>10.77036438261556</v>
+        <v>1.750184212175028</v>
       </c>
       <c r="F7" t="n">
-        <v>10.8313427357807</v>
+        <v>1.760093194564365</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.85632774833969</v>
+        <v>10.7016532591052</v>
       </c>
       <c r="D8" t="n">
-        <v>66.23725925240298</v>
+        <v>10.76355462851548</v>
       </c>
       <c r="E8" t="n">
-        <v>10.77036438261556</v>
+        <v>1.750184212175028</v>
       </c>
       <c r="F8" t="n">
-        <v>10.8313427357807</v>
+        <v>1.760093194564365</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
